--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -1692,11 +1692,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>-171450</xdr:rowOff>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4733925" cy="5000625"/>
+    <xdr:ext cx="4676775" cy="5000625"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="0" name="image2.png" title="Imagine"/>
@@ -5885,34 +5885,34 @@
     <row r="1002" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="F7:K7"/>
+    <mergeCell ref="L7:P7"/>
     <mergeCell ref="T8:T9"/>
     <mergeCell ref="U8:U9"/>
     <mergeCell ref="V8:V9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F7:K7"/>
+    <mergeCell ref="W8:W9"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:W6"/>
+    <mergeCell ref="E7:E9"/>
     <mergeCell ref="Q7:W7"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="E6:W6"/>
-    <mergeCell ref="L7:P7"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
     <mergeCell ref="L8:L9"/>
     <mergeCell ref="M8:M9"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="O8:O9"/>
     <mergeCell ref="L17:P17"/>
-    <mergeCell ref="D8:D9"/>
     <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
